--- a/artfynd/S 296-2024 artfynd.xlsx
+++ b/artfynd/S 296-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127649685</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99976271</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99975954</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99976009</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99976034</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99976068</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99147998</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1549,6 +1589,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99147997</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1668,6 +1713,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99148000</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1791,6 +1841,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99147993</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1910,6 +1965,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99148008</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2029,6 +2089,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99148014</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2147,6 +2212,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91076188</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2244,6 +2314,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88572864</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2341,6 +2416,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88572865</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2438,6 +2518,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88572866</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2544,6 +2629,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88572860</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2641,6 +2731,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88572869</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2747,6 +2842,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88572872</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2853,6 +2953,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88572870</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2950,6 +3055,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88572871</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3047,6 +3157,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81811691</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3144,6 +3259,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81811692</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3241,6 +3361,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82279498</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3342,6 +3467,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82279403</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3439,6 +3569,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82279201</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3536,6 +3671,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82279257</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3633,6 +3773,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82279223</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3730,6 +3875,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82279089</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3832,6 +3982,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82279332</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3934,6 +4089,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82279334</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4036,6 +4196,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82279343</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4138,6 +4303,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82279346</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4240,6 +4410,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82279348</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4342,6 +4517,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82279350</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4439,6 +4619,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82279385</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4545,8 +4730,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888452</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>